--- a/Output/AllModels_SensitivityOtherCovariates_12000.xlsx
+++ b/Output/AllModels_SensitivityOtherCovariates_12000.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="314">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -68,34 +68,34 @@
     <t xml:space="preserve">Intercept</t>
   </si>
   <si>
-    <t xml:space="preserve">0.18***</t>
+    <t xml:space="preserve">0.17***</t>
   </si>
   <si>
     <t xml:space="preserve">[ 0.10,  0.30]</t>
   </si>
   <si>
-    <t xml:space="preserve">29.02***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[23.19, 36.50]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.21***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[90.06, 129.44]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 3.23,  3.89]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.23,   1.62]</t>
+    <t xml:space="preserve">28.30***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[22.65, 35.61]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.89***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[91.53, 129.78]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 3.23,  3.88]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.19,    1.61]</t>
   </si>
   <si>
     <t xml:space="preserve">Within-Person Effects</t>
@@ -104,45 +104,45 @@
     <t xml:space="preserve">Daily individual's experienced persuasion</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.38,  1.83]</t>
+    <t xml:space="preserve">1.59***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.39,  1.84]</t>
   </si>
   <si>
     <t xml:space="preserve">1.03</t>
   </si>
   <si>
+    <t xml:space="preserve">[ 0.98,  1.10]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.00,   1.06]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.03,  0.05]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.67,    1.02]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily partner's experienced persuasion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.17,  1.53]</t>
+  </si>
+  <si>
     <t xml:space="preserve">[ 0.98,  1.08]</t>
   </si>
   <si>
-    <t xml:space="preserve">[ 1.00,   1.06]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.04,  0.04]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.68,   1.03]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily partner's experienced persuasion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.18,  1.53]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.98,  1.07]</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.01</t>
   </si>
   <si>
@@ -155,778 +155,805 @@
     <t xml:space="preserve">[-0.03,  0.06]</t>
   </si>
   <si>
+    <t xml:space="preserve">1.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.83,    1.66]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily individual's experienced pressure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.69,  1.38]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.80,  0.99]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.89,   1.02]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.14,  0.07]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[1.05,    5.47]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily partner's experienced pressure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.05,  2.81]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.86,  1.03]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.92,   1.04]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.13,  0.09]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.55,    5.36]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily individual's experienced pushing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.76,  1.39]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.92,  1.04]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.96,   1.07]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.06,  0.07]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[1.05,    1.89]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily partner's experienced pushing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.05,  1.72]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.91,  1.02]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.96,   1.04]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.07*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.00,  0.13]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.57,    1.38]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.45,  1.03]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.79,  1.10]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.86,   1.03]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.22**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.09,  0.36]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.63,    6.52]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own action plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.57***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 9.34, 14.42]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.24,  1.50]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.02,   1.13]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.03,  0.17]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.41,    1.65]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partner action plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.03,  1.56]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.00,  1.18]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.00,   1.11]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.07,  0.08]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.42,    1.47]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily support received</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily support provided (partner's view)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is a Weekend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.30,  1.93]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.11,  1.28]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.02,   1.11]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.08,  0.21]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.35,    1.01]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JITAI received</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.38,  0.63]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.84,  1.03]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.93*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.88,   0.98]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.12**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.20, -0.03]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.76,    2.92]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days post skilled support intervention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.97,  1.82]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.95,  1.21]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.98,   1.12]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.04,  0.16]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.30,    1.56]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily wear time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.00,   1.00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Between-Person Effects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean individual's experienced persuasion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.62,  3.38]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.75,  1.54]</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.14</t>
   </si>
   <si>
-    <t xml:space="preserve">[0.84,   1.60]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily individual's experienced pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.70,  1.37]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.90*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.81,  1.00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.88,   1.01]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.14,  0.08]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[1.03,   4.87]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily partner's experienced pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.04,  2.74]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.86,  1.04]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.92,   1.05]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.13,  0.10]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.56,   4.71]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily individual's experienced pushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.76,  1.35]</t>
+    <t xml:space="preserve">[ 0.80,   1.62]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.30,  1.11]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.30,   11.04]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean partner's experienced persuasion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.60,  3.23]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.64,  1.31]</t>
   </si>
   <si>
     <t xml:space="preserve">0.99</t>
   </si>
   <si>
-    <t xml:space="preserve">[ 0.92,  1.05]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.96,   1.07]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.06,  0.07]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[1.06,   1.83]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily partner's experienced pushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.05,  1.72]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.90,  1.02]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.96,   1.04]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.07*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.00,  0.14]</t>
+    <t xml:space="preserve">[ 0.68,   1.43]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.38,  1.01]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.34,   16.45]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean individual's experienced pressure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.04,  0.52]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.27,  1.49]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.57,   1.48]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-1.27,  0.60]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.33*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[1.32, 1183.94]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean partner's experienced pressure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.26*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.07,  0.91]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.25,  1.36]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.64,   1.58]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-1.25,  0.61]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.07,   72.52]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean individual's experienced pushing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.39,  5.43]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.77,  2.85]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.56,   1.66]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.97,  1.24]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.05,   29.54]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean partner's experienced pushing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.57,  8.08]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.77,  2.91]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.70,   2.08]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.89,  1.31]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00,    1.11]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean individual's received support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean partner's received support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Difference study group 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.39,  1.64]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.85,  1.43]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.73,   1.17]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.66,  0.24]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.33,    3.97]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Difference study group 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.60,  2.40]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.00,  1.65]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.81,   1.31]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.10,  0.81]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.11,    1.45]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean wear time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Random Effects (Level 3 - Couple)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3:sd(Intercept)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.54, 1.09]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.08, 0.35]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.05, 0.33]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.04, 0.60]</t>
   </si>
   <si>
     <t xml:space="preserve">0.91</t>
   </si>
   <si>
-    <t xml:space="preserve">[0.60,   1.36]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.46,  1.04]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.79,  1.11]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.86,   1.03]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.23**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.08,  0.38]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.69,   6.36]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Own action plan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.49***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 9.35, 14.19]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.24,  1.50]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.02,   1.13]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.05,  0.20]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.42,   1.57]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partner action plan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.01,  1.51]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.99,  1.18]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.00,   1.11]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.10,  0.05]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.46,   1.52]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily support received</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily support provided (partner's view)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Is a Weekend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.29,  1.91]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.10,  1.28]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.01,   1.11]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.08,  0.21]</t>
+    <t xml:space="preserve">[0.10, 1.74]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3:sd(Daily individual's experienced persuasion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.02, 0.41]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.09, 0.19]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.02, 0.08]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.12]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.54]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3:sd(Daily partner's experienced persuasion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.37]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.03, 0.12]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.03, 0.09]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.03, 0.13]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.17, 1.14]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3:sd(Daily individual's experienced pressure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.80]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.24]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.14]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.27]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.12, 2.71]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3:sd(Daily partner's experienced pressure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.02, 1.28]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.18]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.11]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.28]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.05, 3.02]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3:sd(Daily individual's experienced pushing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.23, 0.96]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.17]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.16]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.16]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.02, 0.72]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3:sd(Daily partner's experienced pushing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.61]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.09]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.17]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 1.09]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Random Effects (Level 2 - Couple:Person)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Intercept)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.19, 0.62]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.17, 0.35]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.21, 0.36]</t>
   </si>
   <si>
     <t xml:space="preserve">0.61</t>
   </si>
   <si>
-    <t xml:space="preserve">[0.36,   1.02]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JITAI received</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.38,  0.63]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.85,  1.04]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.87,   0.99]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.10*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.20, -0.01]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.77,   2.78]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days post skilled support intervention</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.96,  1.80]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.94,  1.21]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.98,   1.13]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.06,  0.17]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.33,   1.56]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily wear time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.00,   1.00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Between-Person Effects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean individual's experienced persuasion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.65,  3.13]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.72,  1.34]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.82,   1.49]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.15,  0.94]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.42,   6.85]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean partner's experienced persuasion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.60,  2.88]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.68,  1.26]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.73,   1.33]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.28,  0.81]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.46,   9.66]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean individual's experienced pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.05,  0.47]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.33,  1.45]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.72,   1.32]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.81,  0.24]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.37**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[3.22, 617.66]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean partner's experienced pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.08,  0.78]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.25,  1.12]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.73,   1.32]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.82,  0.24]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.10,  24.54]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean individual's experienced pushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.42,  4.73]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.86,  2.52]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.63,   1.47]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.66,  0.87]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.07,   7.13]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean partner's experienced pushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.70,  7.85]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.94,  2.83]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.79,   1.84]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.50,  1.02]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.05*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00,   0.64]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean individual's received support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean partner's received support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Difference study group 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.39,  1.60]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.81,  1.38]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.73,   1.20]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.66,  0.24]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.36,   3.27]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Difference study group 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.59,  2.33]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.97,  1.60]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.80,   1.33]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.10,  0.80]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.11,   1.21]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean wear time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Random Effects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sd(Intercept)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.63, 1.12]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.22, 0.40]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.24, 0.40]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.44, 0.74]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.69, 1.83]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sd(Daily individual's experienced persuasion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.03, 0.40]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.08, 0.17]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.02, 0.08]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.10]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.02, 0.57]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sd(Daily partner's experienced persuasion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.36]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.04, 0.13]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.02, 0.09]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.13]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.14, 1.03]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sd(Daily individual's experienced pressure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.78]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.23]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.13]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.25]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.11, 2.49]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sd(Daily partner's experienced pressure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.02, 1.25]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.18]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.11]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.27]</t>
+    <t xml:space="preserve">[0.49, 0.78]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.45, 1.82]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Additional Parameters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sigma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.63, 0.68]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.53, 0.56]</t>
   </si>
   <si>
     <t xml:space="preserve">0.87</t>
   </si>
   <si>
-    <t xml:space="preserve">[0.04, 2.83]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sd(Daily individual's experienced pushing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.21, 0.91]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.16]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.14]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.02, 0.65]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sd(Daily partner's experienced pushing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.59]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.14]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.09]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.16]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.94]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Additional Parameters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sigma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.65, 0.70]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.56, 0.59]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.94, 0.98]</t>
+    <t xml:space="preserve">[0.85, 0.89]</t>
   </si>
 </sst>
 </file>
@@ -1622,179 +1649,179 @@
         <v>69</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="F10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="E11" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="H11" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="J11" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="K11" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>92</v>
       </c>
       <c r="G12" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="I12" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="K12" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="I13" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="J13" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="K13" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="G14" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="K14" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1809,7 +1836,7 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1824,10 +1851,10 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>30</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>123</v>
@@ -1868,7 +1895,7 @@
         <v>134</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>135</v>
@@ -1992,7 +2019,7 @@
         <v>159</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>72</v>
+        <v>145</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>160</v>
@@ -2033,167 +2060,167 @@
         <v>171</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>50</v>
+        <v>172</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>90</v>
+        <v>181</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>50</v>
+        <v>170</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>197</v>
+        <v>158</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>203</v>
+        <v>112</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="J27" s="5" t="s">
         <v>214</v>
       </c>
+      <c r="J27" s="1" t="s">
+        <v>215</v>
+      </c>
       <c r="K27" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2208,7 +2235,7 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2223,84 +2250,84 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>92</v>
+        <v>170</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>161</v>
+        <v>227</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>232</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>32</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>155</v>
@@ -2312,98 +2339,98 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>252</v>
+        <v>203</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>253</v>
       </c>
       <c r="F35" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>255</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>256</v>
@@ -2455,31 +2482,31 @@
         <v>269</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="D37" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="G37" s="1" t="s">
+      <c r="H37" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>265</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>274</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>161</v>
+        <v>227</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>275</v>
@@ -2490,7 +2517,7 @@
         <v>276</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>163</v>
+        <v>237</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>277</v>
@@ -2508,36 +2535,36 @@
         <v>280</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>281</v>
       </c>
       <c r="J38" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="K38" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="D39" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="F39" s="1" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>287</v>
@@ -2549,27 +2576,27 @@
         <v>288</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>173</v>
+        <v>289</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>279</v>
@@ -2578,85 +2605,149 @@
         <v>294</v>
       </c>
       <c r="H40" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="I40" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="J40" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="K40" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="8" t="s">
+      <c r="B42" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="F42" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="G42" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="H42" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="H42" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="I42" s="4" t="s">
+      <c r="I42" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
+      <c r="J42" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="7"/>
+      <c r="A43" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="7"/>
+      <c r="A44" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
     </row>
     <row r="45">
       <c r="A45" s="7"/>
@@ -2670,18 +2761,23 @@
     <row r="48">
       <c r="A48" s="7"/>
     </row>
+    <row r="49">
+      <c r="A49" s="7"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A21:K21"/>
     <mergeCell ref="A33:K33"/>
     <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A43:K43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Output/AllModels_SensitivityOtherCovariates_12000.xlsx
+++ b/Output/AllModels_SensitivityOtherCovariates_12000.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="312">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -80,22 +80,22 @@
     <t xml:space="preserve">[22.65, 35.61]</t>
   </si>
   <si>
-    <t xml:space="preserve">108.89***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[91.53, 129.78]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55***</t>
+    <t xml:space="preserve">108.99***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[91.59, 129.54]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56***</t>
   </si>
   <si>
     <t xml:space="preserve">[ 3.23,  3.88]</t>
   </si>
   <si>
-    <t xml:space="preserve">0.56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.19,    1.61]</t>
+    <t xml:space="preserve">0.57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.19,    1.63]</t>
   </si>
   <si>
     <t xml:space="preserve">Within-Person Effects</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">[ 0.98,  1.10]</t>
   </si>
   <si>
-    <t xml:space="preserve">[ 1.00,   1.06]</t>
+    <t xml:space="preserve">[ 0.99,   1.05]</t>
   </si>
   <si>
     <t xml:space="preserve">0.00</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">0.84</t>
   </si>
   <si>
-    <t xml:space="preserve">[0.67,    1.02]</t>
+    <t xml:space="preserve">[0.68,    1.02]</t>
   </si>
   <si>
     <t xml:space="preserve">Daily partner's experienced persuasion</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">1.15</t>
   </si>
   <si>
-    <t xml:space="preserve">[0.83,    1.66]</t>
+    <t xml:space="preserve">[0.83,    1.67]</t>
   </si>
   <si>
     <t xml:space="preserve">Daily individual's experienced pressure</t>
@@ -185,13 +185,13 @@
     <t xml:space="preserve">-0.03</t>
   </si>
   <si>
-    <t xml:space="preserve">[-0.14,  0.07]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[1.05,    5.47]</t>
+    <t xml:space="preserve">[-0.14,  0.08]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[1.05,    5.35]</t>
   </si>
   <si>
     <t xml:space="preserve">Daily partner's experienced pressure</t>
@@ -212,13 +212,13 @@
     <t xml:space="preserve">-0.02</t>
   </si>
   <si>
-    <t xml:space="preserve">[-0.13,  0.09]</t>
+    <t xml:space="preserve">[-0.14,  0.09]</t>
   </si>
   <si>
     <t xml:space="preserve">1.48</t>
   </si>
   <si>
-    <t xml:space="preserve">[0.55,    5.36]</t>
+    <t xml:space="preserve">[0.55,    5.31]</t>
   </si>
   <si>
     <t xml:space="preserve">Daily individual's experienced pushing</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">1.38*</t>
   </si>
   <si>
-    <t xml:space="preserve">[1.05,    1.89]</t>
+    <t xml:space="preserve">[1.05,    1.87]</t>
   </si>
   <si>
     <t xml:space="preserve">Daily partner's experienced pushing</t>
@@ -296,16 +296,16 @@
     <t xml:space="preserve">[ 0.86,   1.03]</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22**</t>
+    <t xml:space="preserve">0.23**</t>
   </si>
   <si>
     <t xml:space="preserve">[ 0.09,  0.36]</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.63,    6.52]</t>
+    <t xml:space="preserve">2.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.62,    6.38]</t>
   </si>
   <si>
     <t xml:space="preserve">Own action plan</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">0.83</t>
   </si>
   <si>
-    <t xml:space="preserve">[0.41,    1.65]</t>
+    <t xml:space="preserve">[0.41,    1.66]</t>
   </si>
   <si>
     <t xml:space="preserve">Partner action plan</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">[ 0.84,  1.03]</t>
   </si>
   <si>
-    <t xml:space="preserve">0.93*</t>
+    <t xml:space="preserve">0.93**</t>
   </si>
   <si>
     <t xml:space="preserve">[ 0.88,   0.98]</t>
@@ -434,10 +434,10 @@
     <t xml:space="preserve">[-0.20, -0.03]</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.76,    2.92]</t>
+    <t xml:space="preserve">1.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.77,    2.88]</t>
   </si>
   <si>
     <t xml:space="preserve">Days post skilled support intervention</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">0.06</t>
   </si>
   <si>
-    <t xml:space="preserve">[-0.04,  0.16]</t>
+    <t xml:space="preserve">[-0.05,  0.16]</t>
   </si>
   <si>
     <t xml:space="preserve">0.69</t>
@@ -500,19 +500,19 @@
     <t xml:space="preserve">1.14</t>
   </si>
   <si>
-    <t xml:space="preserve">[ 0.80,   1.62]</t>
+    <t xml:space="preserve">[ 0.80,   1.61]</t>
   </si>
   <si>
     <t xml:space="preserve">0.41</t>
   </si>
   <si>
-    <t xml:space="preserve">[-0.30,  1.11]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.30,   11.04]</t>
+    <t xml:space="preserve">[-0.29,  1.12]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.30,   11.03]</t>
   </si>
   <si>
     <t xml:space="preserve">Mean partner's experienced persuasion</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">0.32</t>
   </si>
   <si>
-    <t xml:space="preserve">[-0.38,  1.01]</t>
+    <t xml:space="preserve">[-0.37,  1.02]</t>
   </si>
   <si>
     <t xml:space="preserve">2.15</t>
   </si>
   <si>
-    <t xml:space="preserve">[0.34,   16.45]</t>
+    <t xml:space="preserve">[0.34,   16.11]</t>
   </si>
   <si>
     <t xml:space="preserve">Mean individual's experienced pressure</t>
@@ -566,16 +566,16 @@
     <t xml:space="preserve">[ 0.57,   1.48]</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-1.27,  0.60]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.33*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[1.32, 1183.94]</t>
+    <t xml:space="preserve">-0.34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-1.28,  0.60]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.63*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[1.33, 1230.89]</t>
   </si>
   <si>
     <t xml:space="preserve">Mean partner's experienced pressure</t>
@@ -599,13 +599,13 @@
     <t xml:space="preserve">-0.31</t>
   </si>
   <si>
-    <t xml:space="preserve">[-1.25,  0.61]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.07,   72.52]</t>
+    <t xml:space="preserve">[-1.26,  0.62]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.07,   72.50]</t>
   </si>
   <si>
     <t xml:space="preserve">Mean individual's experienced pushing</t>
@@ -620,16 +620,16 @@
     <t xml:space="preserve">[ 0.77,  2.85]</t>
   </si>
   <si>
-    <t xml:space="preserve">[ 0.56,   1.66]</t>
+    <t xml:space="preserve">[ 0.56,   1.68]</t>
   </si>
   <si>
     <t xml:space="preserve">0.13</t>
   </si>
   <si>
-    <t xml:space="preserve">[-0.97,  1.24]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.05,   29.54]</t>
+    <t xml:space="preserve">[-0.96,  1.24]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.05,   28.96]</t>
   </si>
   <si>
     <t xml:space="preserve">Mean partner's experienced pushing</t>
@@ -641,130 +641,127 @@
     <t xml:space="preserve">[ 0.57,  8.08]</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50</t>
-  </si>
-  <si>
     <t xml:space="preserve">[ 0.77,  2.91]</t>
   </si>
   <si>
     <t xml:space="preserve">1.21</t>
   </si>
   <si>
-    <t xml:space="preserve">[ 0.70,   2.08]</t>
+    <t xml:space="preserve">[ 0.70,   2.10]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.88,  1.30]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00,    1.03]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean individual's received support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean partner's received support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Difference study group 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.39,  1.64]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.85,  1.43]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.72,   1.17]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.66,  0.24]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.32,    3.94]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Difference study group 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.60,  2.40]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.00,  1.65]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.81,   1.32]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.10,  0.82]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.10,    1.46]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean wear time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Random Effects (Level 3 - Couple)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3:sd(Intercept)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.54, 1.09]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.08, 0.35]</t>
   </si>
   <si>
     <t xml:space="preserve">0.21</t>
   </si>
   <si>
-    <t xml:space="preserve">[-0.89,  1.31]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00,    1.11]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean individual's received support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean partner's received support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Difference study group 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.39,  1.64]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.85,  1.43]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.73,   1.17]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.66,  0.24]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.33,    3.97]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Difference study group 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.60,  2.40]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.00,  1.65]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.81,   1.31]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.10,  0.81]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.11,    1.45]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean wear time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Random Effects (Level 3 - Couple)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Intercept)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.54, 1.09]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.08, 0.35]</t>
-  </si>
-  <si>
     <t xml:space="preserve">[0.05, 0.33]</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.04, 0.60]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.10, 1.74]</t>
+    <t xml:space="preserve">0.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.03, 0.59]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.09, 1.74]</t>
   </si>
   <si>
     <t xml:space="preserve">L3:sd(Daily individual's experienced persuasion)</t>
@@ -788,7 +785,7 @@
     <t xml:space="preserve">0.20</t>
   </si>
   <si>
-    <t xml:space="preserve">[0.01, 0.54]</t>
+    <t xml:space="preserve">[0.01, 0.53]</t>
   </si>
   <si>
     <t xml:space="preserve">L3:sd(Daily partner's experienced persuasion)</t>
@@ -812,13 +809,10 @@
     <t xml:space="preserve">0.08</t>
   </si>
   <si>
-    <t xml:space="preserve">[0.03, 0.13]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.17, 1.14]</t>
+    <t xml:space="preserve">[0.02, 0.13]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.17, 1.13]</t>
   </si>
   <si>
     <t xml:space="preserve">L3:sd(Daily individual's experienced pressure)</t>
@@ -836,30 +830,30 @@
     <t xml:space="preserve">0.09</t>
   </si>
   <si>
+    <t xml:space="preserve">[0.00, 0.28]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.11, 2.67]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3:sd(Daily partner's experienced pressure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.02, 1.28]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.18]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.11]</t>
+  </si>
+  <si>
     <t xml:space="preserve">[0.00, 0.27]</t>
   </si>
   <si>
-    <t xml:space="preserve">[0.12, 2.71]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced pressure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.02, 1.28]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.18]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.11]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.28]</t>
-  </si>
-  <si>
     <t xml:space="preserve">[0.05, 3.02]</t>
   </si>
   <si>
@@ -875,10 +869,10 @@
     <t xml:space="preserve">[0.01, 0.17]</t>
   </si>
   <si>
-    <t xml:space="preserve">[0.01, 0.16]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.16]</t>
+    <t xml:space="preserve">[0.02, 0.16]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.15]</t>
   </si>
   <si>
     <t xml:space="preserve">0.29</t>
@@ -923,7 +917,7 @@
     <t xml:space="preserve">[0.21, 0.36]</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61</t>
+    <t xml:space="preserve">0.62</t>
   </si>
   <si>
     <t xml:space="preserve">[0.49, 0.78]</t>
@@ -2130,7 +2124,7 @@
         <v>192</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>193</v>
@@ -2194,33 +2188,33 @@
         <v>208</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="G27" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="H27" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="I27" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="J27" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="K27" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2235,7 +2229,7 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2250,77 +2244,77 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>223</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>170</v>
       </c>
       <c r="G30" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="I30" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="J30" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="K30" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="D31" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="E31" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>233</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>32</v>
       </c>
       <c r="G31" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="I31" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="J31" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="K31" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2339,57 +2333,57 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="E34" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="F34" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>246</v>
@@ -2401,350 +2395,350 @@
         <v>248</v>
       </c>
       <c r="J34" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="K34" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>252</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>203</v>
       </c>
       <c r="E35" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="G35" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>255</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>149</v>
       </c>
       <c r="I35" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="J35" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="J35" s="1" t="s">
+      <c r="K35" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>263</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>149</v>
       </c>
       <c r="G36" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="I36" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="J36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K36" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C37" s="1" t="s">
+      <c r="F37" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="E37" s="1" t="s">
+      <c r="H37" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="G37" s="1" t="s">
+      <c r="I37" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="J37" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="K37" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>149</v>
       </c>
       <c r="E38" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="H38" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="J38" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K38" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="D39" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="F39" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>287</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>149</v>
       </c>
       <c r="I39" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="D40" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="H40" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="I40" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G40" s="1" t="s">
+      <c r="J40" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="K40" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C42" s="1" t="s">
+      <c r="F42" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="E42" s="1" t="s">
+      <c r="G42" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="H42" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="I42" s="1" t="s">
         <v>302</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>304</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>112</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="F44" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="G44" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="H44" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="I44" s="4" t="s">
         <v>311</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>313</v>
       </c>
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>

--- a/Output/AllModels_SensitivityOtherCovariates_12000.xlsx
+++ b/Output/AllModels_SensitivityOtherCovariates_12000.xlsx
@@ -1,961 +1,968 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kueng\DataAnalysis\02TimeAndTiesControl\Output\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39949E9-88BE-465F-81F4-5BA30CE98DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="312">
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Subjective MVPA Hurdle Lognormal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Device-Based MVPA Log (Gaussian)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mood Gaussian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reactance Dichotome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hurdle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-Zero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exp(Est.)_hu pa_sub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI_hu pa_sub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exp(Est.)_nonzero pa_sub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI_nonzero pa_sub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exp(Est.) pa_obj_log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI pa_obj_log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Est. mood_gauss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI mood_gauss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OR is_reactance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI is_reactance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intercept</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.17***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.10,  0.30]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.30***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[22.65, 35.61]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.99***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[91.59, 129.54]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 3.23,  3.88]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.19,    1.63]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Within-Person Effects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily individual's experienced persuasion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.39,  1.84]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.98,  1.10]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.99,   1.05]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.03,  0.05]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.68,    1.02]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily partner's experienced persuasion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.17,  1.53]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.98,  1.08]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.98,   1.05]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.03,  0.06]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.83,    1.67]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily individual's experienced pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.69,  1.38]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.80,  0.99]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.89,   1.02]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.14,  0.08]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[1.05,    5.35]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily partner's experienced pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.05,  2.81]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.86,  1.03]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.92,   1.04]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.14,  0.09]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.55,    5.31]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily individual's experienced pushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.76,  1.39]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.92,  1.04]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.96,   1.07]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.06,  0.07]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[1.05,    1.87]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily partner's experienced pushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.05,  1.72]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.91,  1.02]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.96,   1.04]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.07*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.00,  0.13]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.57,    1.38]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.45,  1.03]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.79,  1.10]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.86,   1.03]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.23**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.09,  0.36]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.62,    6.38]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Own action plan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.57***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 9.34, 14.42]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.24,  1.50]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.02,   1.13]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.03,  0.17]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.41,    1.66]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partner action plan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.03,  1.56]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.00,  1.18]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.00,   1.11]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.07,  0.08]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.42,    1.47]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily support received</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily support provided (partner's view)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Is a Weekend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.30,  1.93]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.11,  1.28]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.02,   1.11]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.08,  0.21]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.35,    1.01]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JITAI received</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.38,  0.63]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.84,  1.03]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.88,   0.98]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.12**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.20, -0.03]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.77,    2.88]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days post skilled support intervention</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.97,  1.82]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.95,  1.21]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.98,   1.12]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.05,  0.16]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.30,    1.56]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily wear time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.00,   1.00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Between-Person Effects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean individual's experienced persuasion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.62,  3.38]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.75,  1.54]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.80,   1.61]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.29,  1.12]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.30,   11.03]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean partner's experienced persuasion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.60,  3.23]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.64,  1.31]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.68,   1.43]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.37,  1.02]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.34,   16.11]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean individual's experienced pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.04,  0.52]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.27,  1.49]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.57,   1.48]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-1.28,  0.60]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.63*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[1.33, 1230.89]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean partner's experienced pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.07,  0.91]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.25,  1.36]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.64,   1.58]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-1.26,  0.62]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.07,   72.50]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean individual's experienced pushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.39,  5.43]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.77,  2.85]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.56,   1.68]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.96,  1.24]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.05,   28.96]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean partner's experienced pushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.57,  8.08]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.77,  2.91]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.70,   2.10]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.88,  1.30]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00,    1.03]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean individual's received support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean partner's received support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Difference study group 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.39,  1.64]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.85,  1.43]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.72,   1.17]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.66,  0.24]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.32,    3.94]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Difference study group 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.60,  2.40]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.00,  1.65]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.81,   1.32]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.10,  0.82]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.10,    1.46]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean wear time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Random Effects (Level 3 - Couple)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Intercept)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.54, 1.09]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.08, 0.35]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.05, 0.33]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.03, 0.59]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.09, 1.74]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced persuasion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.02, 0.41]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.09, 0.19]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.02, 0.08]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.12]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.53]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced persuasion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.37]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.03, 0.12]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.03, 0.09]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.02, 0.13]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.17, 1.13]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced pressure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.80]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.24]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.14]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.28]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.11, 2.67]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced pressure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.02, 1.28]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.18]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.11]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.27]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.05, 3.02]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced pushing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.23, 0.96]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.17]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.02, 0.16]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.15]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.02, 0.72]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced pushing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.61]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.09]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.17]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 1.09]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Random Effects (Level 2 - Couple:Person)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2:sd(Intercept)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.19, 0.62]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.17, 0.35]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.21, 0.36]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.49, 0.78]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.45, 1.82]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Additional Parameters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sigma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.63, 0.68]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.53, 0.56]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.85, 0.89]</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="312">
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Subjective MVPA Hurdle Lognormal</t>
+  </si>
+  <si>
+    <t>Device-Based MVPA Log (Gaussian)</t>
+  </si>
+  <si>
+    <t>Mood Gaussian</t>
+  </si>
+  <si>
+    <t>Reactance Dichotome</t>
+  </si>
+  <si>
+    <t>Hurdle</t>
+  </si>
+  <si>
+    <t>Non-Zero</t>
+  </si>
+  <si>
+    <t>exp(Est.)_hu pa_sub</t>
+  </si>
+  <si>
+    <t>95% CI_hu pa_sub</t>
+  </si>
+  <si>
+    <t>exp(Est.)_nonzero pa_sub</t>
+  </si>
+  <si>
+    <t>95% CI_nonzero pa_sub</t>
+  </si>
+  <si>
+    <t>exp(Est.) pa_obj_log</t>
+  </si>
+  <si>
+    <t>95% CI pa_obj_log</t>
+  </si>
+  <si>
+    <t>Est. mood_gauss</t>
+  </si>
+  <si>
+    <t>95% CI mood_gauss</t>
+  </si>
+  <si>
+    <t>OR is_reactance</t>
+  </si>
+  <si>
+    <t>95% CI is_reactance</t>
+  </si>
+  <si>
+    <t>Intercept</t>
+  </si>
+  <si>
+    <t>0.17***</t>
+  </si>
+  <si>
+    <t>[ 0.10,  0.30]</t>
+  </si>
+  <si>
+    <t>28.30***</t>
+  </si>
+  <si>
+    <t>[22.65, 35.61]</t>
+  </si>
+  <si>
+    <t>108.99***</t>
+  </si>
+  <si>
+    <t>[91.59, 129.54]</t>
+  </si>
+  <si>
+    <t>3.56***</t>
+  </si>
+  <si>
+    <t>[ 3.23,  3.88]</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>[0.19,    1.63]</t>
+  </si>
+  <si>
+    <t>Within-Person Effects</t>
+  </si>
+  <si>
+    <t>Daily individual's experienced persuasion</t>
+  </si>
+  <si>
+    <t>1.59***</t>
+  </si>
+  <si>
+    <t>[ 1.39,  1.84]</t>
+  </si>
+  <si>
+    <t>1.03</t>
+  </si>
+  <si>
+    <t>[ 0.98,  1.10]</t>
+  </si>
+  <si>
+    <t>[ 0.99,   1.05]</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>[-0.03,  0.05]</t>
+  </si>
+  <si>
+    <t>0.84</t>
+  </si>
+  <si>
+    <t>[0.68,    1.02]</t>
+  </si>
+  <si>
+    <t>Daily partner's experienced persuasion</t>
+  </si>
+  <si>
+    <t>1.33***</t>
+  </si>
+  <si>
+    <t>[ 1.17,  1.53]</t>
+  </si>
+  <si>
+    <t>[ 0.98,  1.08]</t>
+  </si>
+  <si>
+    <t>1.01</t>
+  </si>
+  <si>
+    <t>[ 0.98,   1.05]</t>
+  </si>
+  <si>
+    <t>0.02</t>
+  </si>
+  <si>
+    <t>[-0.03,  0.06]</t>
+  </si>
+  <si>
+    <t>1.15</t>
+  </si>
+  <si>
+    <t>[0.83,    1.67]</t>
+  </si>
+  <si>
+    <t>Daily individual's experienced pressure</t>
+  </si>
+  <si>
+    <t>0.98</t>
+  </si>
+  <si>
+    <t>[ 0.69,  1.38]</t>
+  </si>
+  <si>
+    <t>0.89*</t>
+  </si>
+  <si>
+    <t>[ 0.80,  0.99]</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>[ 0.89,   1.02]</t>
+  </si>
+  <si>
+    <t>-0.03</t>
+  </si>
+  <si>
+    <t>[-0.14,  0.08]</t>
+  </si>
+  <si>
+    <t>2.09*</t>
+  </si>
+  <si>
+    <t>[1.05,    5.35]</t>
+  </si>
+  <si>
+    <t>Daily partner's experienced pressure</t>
+  </si>
+  <si>
+    <t>1.57*</t>
+  </si>
+  <si>
+    <t>[ 1.05,  2.81]</t>
+  </si>
+  <si>
+    <t>[ 0.86,  1.03]</t>
+  </si>
+  <si>
+    <t>[ 0.92,   1.04]</t>
+  </si>
+  <si>
+    <t>-0.02</t>
+  </si>
+  <si>
+    <t>[-0.14,  0.09]</t>
+  </si>
+  <si>
+    <t>1.48</t>
+  </si>
+  <si>
+    <t>[0.55,    5.31]</t>
+  </si>
+  <si>
+    <t>Daily individual's experienced pushing</t>
+  </si>
+  <si>
+    <t>[ 0.76,  1.39]</t>
+  </si>
+  <si>
+    <t>[ 0.92,  1.04]</t>
+  </si>
+  <si>
+    <t>[ 0.96,   1.07]</t>
+  </si>
+  <si>
+    <t>[-0.06,  0.07]</t>
+  </si>
+  <si>
+    <t>1.38*</t>
+  </si>
+  <si>
+    <t>[1.05,    1.87]</t>
+  </si>
+  <si>
+    <t>Daily partner's experienced pushing</t>
+  </si>
+  <si>
+    <t>1.32*</t>
+  </si>
+  <si>
+    <t>[ 1.05,  1.72]</t>
+  </si>
+  <si>
+    <t>0.97</t>
+  </si>
+  <si>
+    <t>[ 0.91,  1.02]</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>[ 0.96,   1.04]</t>
+  </si>
+  <si>
+    <t>0.07*</t>
+  </si>
+  <si>
+    <t>[ 0.00,  0.13]</t>
+  </si>
+  <si>
+    <t>0.89</t>
+  </si>
+  <si>
+    <t>[0.57,    1.38]</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>0.68</t>
+  </si>
+  <si>
+    <t>[ 0.45,  1.03]</t>
+  </si>
+  <si>
+    <t>0.93</t>
+  </si>
+  <si>
+    <t>[ 0.79,  1.10]</t>
+  </si>
+  <si>
+    <t>0.94</t>
+  </si>
+  <si>
+    <t>[ 0.86,   1.03]</t>
+  </si>
+  <si>
+    <t>0.23**</t>
+  </si>
+  <si>
+    <t>[ 0.09,  0.36]</t>
+  </si>
+  <si>
+    <t>2.00</t>
+  </si>
+  <si>
+    <t>[0.62,    6.38]</t>
+  </si>
+  <si>
+    <t>Own action plan</t>
+  </si>
+  <si>
+    <t>11.57***</t>
+  </si>
+  <si>
+    <t>[ 9.34, 14.42]</t>
+  </si>
+  <si>
+    <t>1.37***</t>
+  </si>
+  <si>
+    <t>[ 1.24,  1.50]</t>
+  </si>
+  <si>
+    <t>1.07**</t>
+  </si>
+  <si>
+    <t>[ 1.02,   1.13]</t>
+  </si>
+  <si>
+    <t>0.10**</t>
+  </si>
+  <si>
+    <t>[ 0.03,  0.17]</t>
+  </si>
+  <si>
+    <t>0.83</t>
+  </si>
+  <si>
+    <t>[0.41,    1.66]</t>
+  </si>
+  <si>
+    <t>Partner action plan</t>
+  </si>
+  <si>
+    <t>1.27*</t>
+  </si>
+  <si>
+    <t>[ 1.03,  1.56]</t>
+  </si>
+  <si>
+    <t>1.09</t>
+  </si>
+  <si>
+    <t>[ 1.00,  1.18]</t>
+  </si>
+  <si>
+    <t>1.05*</t>
+  </si>
+  <si>
+    <t>[ 1.00,   1.11]</t>
+  </si>
+  <si>
+    <t>[-0.07,  0.08]</t>
+  </si>
+  <si>
+    <t>0.79</t>
+  </si>
+  <si>
+    <t>[0.42,    1.47]</t>
+  </si>
+  <si>
+    <t>Daily support received</t>
+  </si>
+  <si>
+    <t>Daily support provided (partner's view)</t>
+  </si>
+  <si>
+    <t>Is a Weekend</t>
+  </si>
+  <si>
+    <t>1.58***</t>
+  </si>
+  <si>
+    <t>[ 1.30,  1.93]</t>
+  </si>
+  <si>
+    <t>1.19***</t>
+  </si>
+  <si>
+    <t>[ 1.11,  1.28]</t>
+  </si>
+  <si>
+    <t>1.06**</t>
+  </si>
+  <si>
+    <t>[ 1.02,   1.11]</t>
+  </si>
+  <si>
+    <t>0.15***</t>
+  </si>
+  <si>
+    <t>[ 0.08,  0.21]</t>
+  </si>
+  <si>
+    <t>0.60</t>
+  </si>
+  <si>
+    <t>[0.35,    1.01]</t>
+  </si>
+  <si>
+    <t>JITAI received</t>
+  </si>
+  <si>
+    <t>0.49***</t>
+  </si>
+  <si>
+    <t>[ 0.38,  0.63]</t>
+  </si>
+  <si>
+    <t>[ 0.84,  1.03]</t>
+  </si>
+  <si>
+    <t>0.93**</t>
+  </si>
+  <si>
+    <t>[ 0.88,   0.98]</t>
+  </si>
+  <si>
+    <t>-0.12**</t>
+  </si>
+  <si>
+    <t>[-0.20, -0.03]</t>
+  </si>
+  <si>
+    <t>1.50</t>
+  </si>
+  <si>
+    <t>[0.77,    2.88]</t>
+  </si>
+  <si>
+    <t>Days post skilled support intervention</t>
+  </si>
+  <si>
+    <t>1.32</t>
+  </si>
+  <si>
+    <t>[ 0.97,  1.82]</t>
+  </si>
+  <si>
+    <t>1.07</t>
+  </si>
+  <si>
+    <t>[ 0.95,  1.21]</t>
+  </si>
+  <si>
+    <t>1.05</t>
+  </si>
+  <si>
+    <t>[ 0.98,   1.12]</t>
+  </si>
+  <si>
+    <t>0.06</t>
+  </si>
+  <si>
+    <t>[-0.05,  0.16]</t>
+  </si>
+  <si>
+    <t>0.69</t>
+  </si>
+  <si>
+    <t>[0.30,    1.56]</t>
+  </si>
+  <si>
+    <t>Daily wear time</t>
+  </si>
+  <si>
+    <t>1.00***</t>
+  </si>
+  <si>
+    <t>[ 1.00,   1.00]</t>
+  </si>
+  <si>
+    <t>Between-Person Effects</t>
+  </si>
+  <si>
+    <t>Mean individual's experienced persuasion</t>
+  </si>
+  <si>
+    <t>1.46</t>
+  </si>
+  <si>
+    <t>[ 0.62,  3.38]</t>
+  </si>
+  <si>
+    <t>[ 0.75,  1.54]</t>
+  </si>
+  <si>
+    <t>1.14</t>
+  </si>
+  <si>
+    <t>[ 0.80,   1.61]</t>
+  </si>
+  <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>[-0.29,  1.12]</t>
+  </si>
+  <si>
+    <t>1.72</t>
+  </si>
+  <si>
+    <t>[0.30,   11.03]</t>
+  </si>
+  <si>
+    <t>Mean partner's experienced persuasion</t>
+  </si>
+  <si>
+    <t>1.40</t>
+  </si>
+  <si>
+    <t>[ 0.60,  3.23]</t>
+  </si>
+  <si>
+    <t>0.92</t>
+  </si>
+  <si>
+    <t>[ 0.64,  1.31]</t>
+  </si>
+  <si>
+    <t>0.99</t>
+  </si>
+  <si>
+    <t>[ 0.68,   1.43]</t>
+  </si>
+  <si>
+    <t>0.32</t>
+  </si>
+  <si>
+    <t>[-0.37,  1.02]</t>
+  </si>
+  <si>
+    <t>2.15</t>
+  </si>
+  <si>
+    <t>[0.34,   16.11]</t>
+  </si>
+  <si>
+    <t>Mean individual's experienced pressure</t>
+  </si>
+  <si>
+    <t>0.15**</t>
+  </si>
+  <si>
+    <t>[ 0.04,  0.52]</t>
+  </si>
+  <si>
+    <t>0.63</t>
+  </si>
+  <si>
+    <t>[ 0.27,  1.49]</t>
+  </si>
+  <si>
+    <t>[ 0.57,   1.48]</t>
+  </si>
+  <si>
+    <t>-0.34</t>
+  </si>
+  <si>
+    <t>[-1.28,  0.60]</t>
+  </si>
+  <si>
+    <t>33.63*</t>
+  </si>
+  <si>
+    <t>[1.33, 1230.89]</t>
+  </si>
+  <si>
+    <t>Mean partner's experienced pressure</t>
+  </si>
+  <si>
+    <t>0.26*</t>
+  </si>
+  <si>
+    <t>[ 0.07,  0.91]</t>
+  </si>
+  <si>
+    <t>0.58</t>
+  </si>
+  <si>
+    <t>[ 0.25,  1.36]</t>
+  </si>
+  <si>
+    <t>[ 0.64,   1.58]</t>
+  </si>
+  <si>
+    <t>-0.31</t>
+  </si>
+  <si>
+    <t>[-1.26,  0.62]</t>
+  </si>
+  <si>
+    <t>2.52</t>
+  </si>
+  <si>
+    <t>[0.07,   72.50]</t>
+  </si>
+  <si>
+    <t>Mean individual's experienced pushing</t>
+  </si>
+  <si>
+    <t>[ 0.39,  5.43]</t>
+  </si>
+  <si>
+    <t>1.47</t>
+  </si>
+  <si>
+    <t>[ 0.77,  2.85]</t>
+  </si>
+  <si>
+    <t>[ 0.56,   1.68]</t>
+  </si>
+  <si>
+    <t>0.13</t>
+  </si>
+  <si>
+    <t>[-0.96,  1.24]</t>
+  </si>
+  <si>
+    <t>[0.05,   28.96]</t>
+  </si>
+  <si>
+    <t>Mean partner's experienced pushing</t>
+  </si>
+  <si>
+    <t>2.14</t>
+  </si>
+  <si>
+    <t>[ 0.57,  8.08]</t>
+  </si>
+  <si>
+    <t>[ 0.77,  2.91]</t>
+  </si>
+  <si>
+    <t>1.21</t>
+  </si>
+  <si>
+    <t>[ 0.70,   2.10]</t>
+  </si>
+  <si>
+    <t>0.22</t>
+  </si>
+  <si>
+    <t>[-0.88,  1.30]</t>
+  </si>
+  <si>
+    <t>0.04</t>
+  </si>
+  <si>
+    <t>[0.00,    1.03]</t>
+  </si>
+  <si>
+    <t>Mean individual's received support</t>
+  </si>
+  <si>
+    <t>Mean partner's received support</t>
+  </si>
+  <si>
+    <t>Difference study group 2</t>
+  </si>
+  <si>
+    <t>0.80</t>
+  </si>
+  <si>
+    <t>[ 0.39,  1.64]</t>
+  </si>
+  <si>
+    <t>1.11</t>
+  </si>
+  <si>
+    <t>[ 0.85,  1.43]</t>
+  </si>
+  <si>
+    <t>[ 0.72,   1.17]</t>
+  </si>
+  <si>
+    <t>-0.21</t>
+  </si>
+  <si>
+    <t>[-0.66,  0.24]</t>
+  </si>
+  <si>
+    <t>1.16</t>
+  </si>
+  <si>
+    <t>[0.32,    3.94]</t>
+  </si>
+  <si>
+    <t>Difference study group 3</t>
+  </si>
+  <si>
+    <t>1.18</t>
+  </si>
+  <si>
+    <t>[ 0.60,  2.40]</t>
+  </si>
+  <si>
+    <t>1.30*</t>
+  </si>
+  <si>
+    <t>[ 1.00,  1.65]</t>
+  </si>
+  <si>
+    <t>[ 0.81,   1.32]</t>
+  </si>
+  <si>
+    <t>0.36</t>
+  </si>
+  <si>
+    <t>[-0.10,  0.82]</t>
+  </si>
+  <si>
+    <t>0.39</t>
+  </si>
+  <si>
+    <t>[0.10,    1.46]</t>
+  </si>
+  <si>
+    <t>Mean wear time</t>
+  </si>
+  <si>
+    <t>Random Effects (Level 3 - Couple)</t>
+  </si>
+  <si>
+    <t>L3:sd(Intercept)</t>
+  </si>
+  <si>
+    <t>0.78</t>
+  </si>
+  <si>
+    <t>[0.54, 1.09]</t>
+  </si>
+  <si>
+    <t>0.23</t>
+  </si>
+  <si>
+    <t>[0.08, 0.35]</t>
+  </si>
+  <si>
+    <t>0.21</t>
+  </si>
+  <si>
+    <t>[0.05, 0.33]</t>
+  </si>
+  <si>
+    <t>0.33</t>
+  </si>
+  <si>
+    <t>[0.03, 0.59]</t>
+  </si>
+  <si>
+    <t>[0.09, 1.74]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily individual's experienced persuasion)</t>
+  </si>
+  <si>
+    <t>[0.02, 0.41]</t>
+  </si>
+  <si>
+    <t>[0.09, 0.19]</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>[0.02, 0.08]</t>
+  </si>
+  <si>
+    <t>[0.01, 0.12]</t>
+  </si>
+  <si>
+    <t>0.20</t>
+  </si>
+  <si>
+    <t>[0.01, 0.53]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily partner's experienced persuasion)</t>
+  </si>
+  <si>
+    <t>0.17</t>
+  </si>
+  <si>
+    <t>[0.01, 0.37]</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>[0.03, 0.12]</t>
+  </si>
+  <si>
+    <t>[0.03, 0.09]</t>
+  </si>
+  <si>
+    <t>0.08</t>
+  </si>
+  <si>
+    <t>[0.02, 0.13]</t>
+  </si>
+  <si>
+    <t>[0.17, 1.13]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily individual's experienced pressure)</t>
+  </si>
+  <si>
+    <t>[0.01, 0.80]</t>
+  </si>
+  <si>
+    <t>[0.00, 0.24]</t>
+  </si>
+  <si>
+    <t>[0.00, 0.14]</t>
+  </si>
+  <si>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t>[0.00, 0.28]</t>
+  </si>
+  <si>
+    <t>[0.11, 2.67]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily partner's experienced pressure)</t>
+  </si>
+  <si>
+    <t>[0.02, 1.28]</t>
+  </si>
+  <si>
+    <t>[0.00, 0.18]</t>
+  </si>
+  <si>
+    <t>0.03</t>
+  </si>
+  <si>
+    <t>[0.00, 0.11]</t>
+  </si>
+  <si>
+    <t>[0.00, 0.27]</t>
+  </si>
+  <si>
+    <t>[0.05, 3.02]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily individual's experienced pushing)</t>
+  </si>
+  <si>
+    <t>0.53</t>
+  </si>
+  <si>
+    <t>[0.23, 0.96]</t>
+  </si>
+  <si>
+    <t>[0.01, 0.17]</t>
+  </si>
+  <si>
+    <t>[0.02, 0.16]</t>
+  </si>
+  <si>
+    <t>[0.00, 0.15]</t>
+  </si>
+  <si>
+    <t>0.29</t>
+  </si>
+  <si>
+    <t>[0.02, 0.72]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily partner's experienced pushing)</t>
+  </si>
+  <si>
+    <t>0.24</t>
+  </si>
+  <si>
+    <t>[0.01, 0.61]</t>
+  </si>
+  <si>
+    <t>[0.00, 0.09]</t>
+  </si>
+  <si>
+    <t>[0.00, 0.17]</t>
+  </si>
+  <si>
+    <t>[0.01, 1.09]</t>
+  </si>
+  <si>
+    <t>Random Effects (Level 2 - Couple:Person)</t>
+  </si>
+  <si>
+    <t>L2:sd(Intercept)</t>
+  </si>
+  <si>
+    <t>[0.19, 0.62]</t>
+  </si>
+  <si>
+    <t>[0.17, 0.35]</t>
+  </si>
+  <si>
+    <t>0.27</t>
+  </si>
+  <si>
+    <t>[0.21, 0.36]</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>[0.49, 0.78]</t>
+  </si>
+  <si>
+    <t>[0.45, 1.82]</t>
+  </si>
+  <si>
+    <t>Additional Parameters</t>
+  </si>
+  <si>
+    <t>sigma</t>
+  </si>
+  <si>
+    <t>0.65</t>
+  </si>
+  <si>
+    <t>[0.63, 0.68]</t>
+  </si>
+  <si>
+    <t>0.54</t>
+  </si>
+  <si>
+    <t>[0.53, 0.56]</t>
+  </si>
+  <si>
+    <t>0.87</t>
+  </si>
+  <si>
+    <t>[0.85, 0.89]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -969,16 +976,16 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <b/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <i/>
     </font>
   </fonts>
   <fills count="2">
@@ -998,20 +1005,28 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1024,20 +1039,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1319,46 +1349,59 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K50"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1393,7 +1436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1428,7 +1471,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1463,43 +1506,43 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -1533,8 +1576,8 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -1568,8 +1611,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -1603,8 +1646,8 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="7" t="s">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
         <v>60</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -1638,8 +1681,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
         <v>69</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -1673,8 +1716,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
         <v>76</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -1708,8 +1751,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
         <v>87</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -1743,8 +1786,8 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
         <v>98</v>
       </c>
       <c r="B13" s="5" t="s">
@@ -1778,8 +1821,8 @@
         <v>108</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>109</v>
       </c>
       <c r="B14" s="5" t="s">
@@ -1813,8 +1856,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>119</v>
       </c>
       <c r="B15" s="1"/>
@@ -1828,8 +1871,8 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
         <v>120</v>
       </c>
       <c r="B16" s="1"/>
@@ -1843,8 +1886,8 @@
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>121</v>
       </c>
       <c r="B17" s="5" t="s">
@@ -1878,8 +1921,8 @@
         <v>131</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>132</v>
       </c>
       <c r="B18" s="5" t="s">
@@ -1913,8 +1956,8 @@
         <v>141</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>142</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -1948,8 +1991,8 @@
         <v>152</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>153</v>
       </c>
       <c r="B20" s="1"/>
@@ -1967,43 +2010,43 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I21" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="J21" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="K21" s="10" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
         <v>157</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -2037,8 +2080,8 @@
         <v>166</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="s">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
         <v>167</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -2072,8 +2115,8 @@
         <v>177</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="s">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
         <v>178</v>
       </c>
       <c r="B24" s="5" t="s">
@@ -2107,8 +2150,8 @@
         <v>187</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="7" t="s">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
         <v>188</v>
       </c>
       <c r="B25" s="5" t="s">
@@ -2142,8 +2185,8 @@
         <v>197</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="7" t="s">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
         <v>198</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -2177,8 +2220,8 @@
         <v>205</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="7" t="s">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
         <v>206</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -2212,8 +2255,8 @@
         <v>215</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="s">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
         <v>216</v>
       </c>
       <c r="B28" s="1"/>
@@ -2227,8 +2270,8 @@
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
     </row>
-    <row r="29">
-      <c r="A29" s="7" t="s">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
         <v>217</v>
       </c>
       <c r="B29" s="1"/>
@@ -2242,8 +2285,8 @@
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
     </row>
-    <row r="30">
-      <c r="A30" s="7" t="s">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
         <v>218</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -2277,8 +2320,8 @@
         <v>227</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="7" t="s">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
         <v>228</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -2312,8 +2355,8 @@
         <v>237</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="7" t="s">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
         <v>238</v>
       </c>
       <c r="B32" s="1"/>
@@ -2331,43 +2374,43 @@
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
     </row>
-    <row r="33">
-      <c r="A33" s="6" t="s">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="H33" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="I33" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="J33" s="1" t="s">
+      <c r="J33" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="K33" s="10" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="7" t="s">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
         <v>240</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -2401,8 +2444,8 @@
         <v>249</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="7" t="s">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
         <v>250</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -2436,8 +2479,8 @@
         <v>257</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="7" t="s">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
         <v>258</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -2471,8 +2514,8 @@
         <v>266</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="7" t="s">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
         <v>267</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -2506,8 +2549,8 @@
         <v>273</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="7" t="s">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
         <v>274</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -2541,8 +2584,8 @@
         <v>280</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="7" t="s">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
         <v>281</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -2576,8 +2619,8 @@
         <v>288</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="7" t="s">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
         <v>289</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -2611,43 +2654,43 @@
         <v>294</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="6" t="s">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="I41" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="J41" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="K41" s="10" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="s">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
         <v>296</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -2681,43 +2724,43 @@
         <v>303</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="6" t="s">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="H43" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="I43" s="1" t="s">
+      <c r="I43" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="J43" s="1" t="s">
+      <c r="J43" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="K43" s="1" t="s">
+      <c r="K43" s="10" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="8" t="s">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="7" t="s">
         <v>305</v>
       </c>
       <c r="B44" s="4"/>
@@ -2743,37 +2786,37 @@
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
     </row>
-    <row r="45">
-      <c r="A45" s="7"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="7"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="7"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="7"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="7"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="7"/>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="6"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="6"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="6"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="6"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="6"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A43:K43"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A21:K21"/>
-    <mergeCell ref="A33:K33"/>
-    <mergeCell ref="A41:K41"/>
-    <mergeCell ref="A43:K43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/Output/AllModels_SensitivityOtherCovariates_12000.xlsx
+++ b/Output/AllModels_SensitivityOtherCovariates_12000.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="315">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -764,24 +764,6 @@
     <t xml:space="preserve">[0.05, 1.61]</t>
   </si>
   <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced persuasion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced persuasion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced pressure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced pressure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced pushing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced pushing)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Random Effects (Level 2 - Couple:Person)</t>
   </si>
   <si>
@@ -816,6 +798,147 @@
   </si>
   <si>
     <t xml:space="preserve">[0.47, 2.12]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily individual's experienced persuasion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.12, 0.57]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.09, 0.17]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.03, 0.09]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.04, 0.14]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.03, 0.71]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily partner's experienced persuasion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.15, 0.59]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.02, 0.12]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.03, 0.10]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.13]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.15, 1.13]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily individual's experienced pressure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.02, 1.32]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.22]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.12]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.23]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.40, 3.28]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily partner's experienced pressure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.03, 2.00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.18]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.13]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.24]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.04, 3.32]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily individual's experienced pushing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.24, 1.23]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.15]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.14]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.69]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily partner's experienced pushing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.02, 0.88]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.10]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.14]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.87]</t>
   </si>
   <si>
     <t xml:space="preserve">Additional Parameters</t>
@@ -897,7 +1020,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -915,6 +1038,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
@@ -2288,203 +2414,323 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
+      <c r="B35" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
+      <c r="B36" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
+        <v>262</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
+        <v>272</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
+        <v>281</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
+        <v>288</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="s">
-        <v>256</v>
+      <c r="A41" s="7" t="s">
+        <v>295</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>256</v>
+        <v>296</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>256</v>
+        <v>150</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>256</v>
+        <v>298</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>256</v>
+        <v>299</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>256</v>
+        <v>150</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>256</v>
+        <v>298</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>256</v>
+        <v>300</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>256</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="s">
-        <v>257</v>
+        <v>302</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>258</v>
+        <v>303</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>259</v>
+        <v>304</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>263</v>
+        <v>305</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>264</v>
+        <v>150</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>265</v>
+        <v>306</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>267</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="s">
-        <v>268</v>
+        <v>309</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>268</v>
+        <v>309</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>268</v>
+        <v>309</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>268</v>
+        <v>309</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>268</v>
+        <v>309</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>268</v>
+        <v>309</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>268</v>
+        <v>309</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>268</v>
+        <v>309</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>268</v>
+        <v>309</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>268</v>
+        <v>309</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>268</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="s">
-        <v>269</v>
+      <c r="A44" s="9" t="s">
+        <v>310</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -2492,19 +2738,19 @@
         <v>152</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>270</v>
+        <v>311</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>271</v>
+        <v>312</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>272</v>
+        <v>313</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>273</v>
+        <v>314</v>
       </c>
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
@@ -2536,7 +2782,7 @@
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A21:K21"/>
     <mergeCell ref="A33:K33"/>
-    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A35:K35"/>
     <mergeCell ref="A43:K43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
